--- a/results/04_final_refined_daily_hydroclimate_data/601/Dry_bulb_temp_06h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/601/Dry_bulb_temp_06h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -553,8 +553,8 @@
       <c r="C12">
         <v>11</v>
       </c>
-      <c r="D12" t="s">
-        <v>4</v>
+      <c r="D12">
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -567,8 +567,8 @@
       <c r="C13">
         <v>12</v>
       </c>
-      <c r="D13" t="s">
-        <v>4</v>
+      <c r="D13">
+        <v>15.1</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -581,8 +581,8 @@
       <c r="C14">
         <v>13</v>
       </c>
-      <c r="D14" t="s">
-        <v>4</v>
+      <c r="D14">
+        <v>15.4</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -595,8 +595,8 @@
       <c r="C15">
         <v>14</v>
       </c>
-      <c r="D15" t="s">
-        <v>4</v>
+      <c r="D15">
+        <v>16.2</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -609,8 +609,8 @@
       <c r="C16">
         <v>15</v>
       </c>
-      <c r="D16" t="s">
-        <v>4</v>
+      <c r="D16">
+        <v>15.5</v>
       </c>
     </row>
     <row r="17" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/601/Dry_bulb_temp_06h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/601/Dry_bulb_temp_06h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -623,8 +623,8 @@
       <c r="C17">
         <v>16</v>
       </c>
-      <c r="D17" t="s">
-        <v>4</v>
+      <c r="D17">
+        <v>15.1</v>
       </c>
     </row>
     <row r="18" spans="1:4">
